--- a/帝国时代2决定版 文明联盟 巨型投石机流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 巨型投石机流最优研究顺序 By RemonBo.xlsx
@@ -73,7 +73,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -88,11 +88,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFE9CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF7CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -132,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -152,13 +147,10 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -702,21 +694,13 @@
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>阿兹特克（备选）</t>
-        </is>
-      </c>
+      <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="4" t="inlineStr"/>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="2" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>阿兹特克（备选）</t>
-        </is>
-      </c>
+      <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="4" t="inlineStr"/>
       <c r="D12" s="4" t="inlineStr"/>
     </row>
@@ -954,7 +938,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -981,7 +965,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -1008,7 +992,7 @@
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -1033,9 +1017,9 @@
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -1055,14 +1039,14 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -1082,14 +1066,14 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>直接强化巨型投石机</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>额外一次的投掷/发射，等于直接翻倍输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1109,7 +1093,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>直接强化巨型投石机</t>
+          <t>提升命中率与对移动目标的准确度，减少空枪</t>
         </is>
       </c>
     </row>
@@ -1164,9 +1148,9 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -2734,7 +2718,7 @@
           <t>鞑靼</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -2744,7 +2728,7 @@
           <t>免费位</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>帖木儿攻城术（巨型投石机射程+2）</t>
         </is>
@@ -2764,7 +2748,7 @@
           <t>不列颠</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -2774,7 +2758,7 @@
           <t>免费位</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>战狼号（巨型投石机可造成爆炸伤害且更准）</t>
         </is>
@@ -2794,7 +2778,7 @@
           <t>日本</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -2804,7 +2788,7 @@
           <t>免费位</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>弹射器（巨型投石机攻速和组装/拆装提升）</t>
         </is>
@@ -2834,7 +2818,7 @@
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>配重块（巨型投石机/投石车系攻+15%）</t>
         </is>
@@ -2864,7 +2848,7 @@
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>卧虎（牵引抛石机/楼船巨型投石武器发更多弹药）</t>
         </is>
@@ -2894,7 +2878,7 @@
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>牵引抛石机/楼船费用-25%</t>
         </is>
@@ -2924,7 +2908,7 @@
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>巨型投石机攻单位/小目标更准</t>
         </is>
@@ -2944,7 +2928,7 @@
           <t>阿兹特克</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -2954,7 +2938,7 @@
           <t>不建议</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>无一条直接加强巨型投石机</t>
         </is>
@@ -2974,7 +2958,7 @@
           <t>埃塞俄比亚</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -2984,7 +2968,7 @@
           <t>不建议</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>无一条直接加强巨型投石机</t>
         </is>
@@ -3004,7 +2988,7 @@
           <t>柏柏尔</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3014,7 +2998,7 @@
           <t>不建议</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>无一条直接加强巨型投石机</t>
         </is>
@@ -3034,7 +3018,7 @@
           <t>拜占庭</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3064,7 +3048,7 @@
           <t>保加利亚</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3094,7 +3078,7 @@
           <t>波兰</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3124,7 +3108,7 @@
           <t>波斯</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3154,7 +3138,7 @@
           <t>波希米亚</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3184,7 +3168,7 @@
           <t>勃艮第</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3214,7 +3198,7 @@
           <t>达罗毗荼</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3244,7 +3228,7 @@
           <t>丹麦人</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3274,7 +3258,7 @@
           <t>法兰克</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3304,7 +3288,7 @@
           <t>高丽</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3334,7 +3318,7 @@
           <t>高棉</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3364,7 +3348,7 @@
           <t>哥特</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3394,7 +3378,7 @@
           <t>格鲁吉亚</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3424,7 +3408,7 @@
           <t>凯尔特</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3454,7 +3438,7 @@
           <t>库曼</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3484,7 +3468,7 @@
           <t>立陶宛</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3514,7 +3498,7 @@
           <t>罗马</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3544,7 +3528,7 @@
           <t>马来</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3574,7 +3558,7 @@
           <t>马里</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3604,7 +3588,7 @@
           <t>马普切</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3634,7 +3618,7 @@
           <t>马扎尔</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3664,7 +3648,7 @@
           <t>玛雅</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3694,7 +3678,7 @@
           <t>蒙古</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3724,7 +3708,7 @@
           <t>孟加拉</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3754,7 +3738,7 @@
           <t>缅甸</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3784,7 +3768,7 @@
           <t>穆伊斯卡</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3814,7 +3798,7 @@
           <t>女真</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3844,7 +3828,7 @@
           <t>葡萄牙</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3874,7 +3858,7 @@
           <t>契丹</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3904,7 +3888,7 @@
           <t>瞿折罗</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3934,7 +3918,7 @@
           <t>撒克逊人</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3964,7 +3948,7 @@
           <t>蜀</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3994,7 +3978,7 @@
           <t>斯拉夫</t>
         </is>
       </c>
-      <c r="C44" s="9" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4024,7 +4008,7 @@
           <t>条顿</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4054,7 +4038,7 @@
           <t>图皮</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4084,7 +4068,7 @@
           <t>土耳其</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4114,7 +4098,7 @@
           <t>瓦兰吉人</t>
         </is>
       </c>
-      <c r="C48" s="9" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4144,7 +4128,7 @@
           <t>维京</t>
         </is>
       </c>
-      <c r="C49" s="9" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4174,7 +4158,7 @@
           <t>西班牙</t>
         </is>
       </c>
-      <c r="C50" s="9" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4204,7 +4188,7 @@
           <t>西西里</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4234,7 +4218,7 @@
           <t>亚美尼亚</t>
         </is>
       </c>
-      <c r="C52" s="9" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4264,7 +4248,7 @@
           <t>意大利</t>
         </is>
       </c>
-      <c r="C53" s="9" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4294,7 +4278,7 @@
           <t>印度斯坦</t>
         </is>
       </c>
-      <c r="C54" s="9" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4324,7 +4308,7 @@
           <t>印加</t>
         </is>
       </c>
-      <c r="C55" s="9" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4354,7 +4338,7 @@
           <t>越南</t>
         </is>
       </c>
-      <c r="C56" s="9" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4384,7 +4368,7 @@
           <t>中国</t>
         </is>
       </c>
-      <c r="C57" s="9" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4414,7 +4398,7 @@
           <t>阿契美尼德</t>
         </is>
       </c>
-      <c r="C58" s="9" t="inlineStr">
+      <c r="C58" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4444,7 +4428,7 @@
           <t>马其顿人</t>
         </is>
       </c>
-      <c r="C59" s="9" t="inlineStr">
+      <c r="C59" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4474,7 +4458,7 @@
           <t>普鲁人</t>
         </is>
       </c>
-      <c r="C60" s="9" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4504,7 +4488,7 @@
           <t>色雷斯人</t>
         </is>
       </c>
-      <c r="C61" s="9" t="inlineStr">
+      <c r="C61" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4534,7 +4518,7 @@
           <t>斯巴达</t>
         </is>
       </c>
-      <c r="C62" s="9" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4564,7 +4548,7 @@
           <t>雅典</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4606,212 +4590,212 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>《帝国时代2 决定版》巨型投石机流最优研究顺序</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>By RemonBo</t>
         </is>
       </c>
     </row>
     <row r="2" ht="19" customHeight="1">
-      <c r="A2" s="12" t="inlineStr"/>
-      <c r="B2" s="11" t="inlineStr"/>
+      <c r="A2" s="11" t="inlineStr"/>
+      <c r="B2" s="10" t="inlineStr"/>
     </row>
     <row r="3" ht="19" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>口径</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>62 个按钮 = 各文明的全部特性（主要功能 + 独特科技 + 团队加成），不含独特单位。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="19" customHeight="1">
-      <c r="A4" s="11" t="inlineStr"/>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr"/>
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>团队加成按「对自己生效」计算，不因原本是全队加成而降权。</t>
         </is>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1">
-      <c r="A5" s="11" t="inlineStr"/>
-      <c r="B5" s="11" t="inlineStr"/>
+      <c r="A5" s="10" t="inlineStr"/>
+      <c r="B5" s="10" t="inlineStr"/>
     </row>
     <row r="6" ht="19" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>决定性前提 1</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>巨型投石机出自城堡，是攻坚建筑的第一答案，但移动与组装极慢。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>决定性前提 2</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>拆装速度与射程决定它是安全输出还是送菜；弹射器/配重块类专有科技价值最高。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>决定性前提 3</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>必须有部队与城堡保护，它单挑不过任何近战。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1">
-      <c r="A9" s="11" t="inlineStr"/>
-      <c r="B9" s="11" t="inlineStr"/>
+      <c r="A9" s="10" t="inlineStr"/>
+      <c r="B9" s="10" t="inlineStr"/>
     </row>
     <row r="10" ht="19" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>模组专属：按钮机制</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>开局 3 个免费按钮位；之后每个按钮 2000 金。一个按钮只能研究一次，重复研究等于白花。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>模组专属：攻城 SSR</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>「攻城SSR：提升弩炮等攻城武器的攻速和移速，并禁用塔防SSR」——对巨型投石机同样有效。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>排序口径</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>① 只看直接作用于巨型投石机本体、或其前置/费用/产出的条目；</t>
         </is>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="11" t="inlineStr"/>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr"/>
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>② 泛用条目与兵种类一律剔除（放进「与巨型投石机流无关·可跳过」）；</t>
         </is>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="11" t="inlineStr"/>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr"/>
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>③ 门槛越低、替代成本越高，名次越靠前。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="11" t="inlineStr"/>
-      <c r="B15" s="11" t="inlineStr"/>
+      <c r="A15" s="10" t="inlineStr"/>
+      <c r="B15" s="10" t="inlineStr"/>
     </row>
     <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>未验证项</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>本表的档位与名次为依据「条目文本 + 官方科技树」的经验判断，未逐项实测；与实战不符时以实战为准。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>★ 最重要的一条：别买重复</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>主选文明已经自带的加成，不要再用按钮买一遍——一个按钮只能研究一次，重复等于白花 2000 金。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="11" t="inlineStr"/>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr"/>
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>正确流程是：先定主选文明（见「主选文明推荐」），再按剩下的缺口挑 3 个免费位。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>数据来源</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="11" t="inlineStr"/>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr"/>
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>整理</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>By RemonBo；本表由 DSH 生成。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>与本表配套</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>同目录下的箭塔流、炮塔流与其余流派总表。</t>
         </is>

--- a/帝国时代2决定版 文明联盟 巨型投石机流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 巨型投石机流最优研究顺序 By RemonBo.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开局3免费位" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="后续2000金顺序" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="甲类·巨型投石机本体强化" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乙类·费用与前置" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乙类·减费用与资源效率" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="与巨型投石机流无关·可跳过" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主选文明推荐" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全62文明总名次" sheetId="7" state="visible" r:id="rId7"/>
@@ -18,15 +18,15 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·巨型投石机本体强化'!$A$1:$E$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·巨型投石机本体强化'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·费用与前置'!$A$1:$E$2</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·费用与前置'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与巨型投石机流无关·可跳过'!$A$1:$D$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·减费用与资源效率'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与巨型投石机流无关·可跳过'!$A$1:$D$55</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'与巨型投石机流无关·可跳过'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'主选文明推荐'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'主选文明推荐'!$A$1:$E$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'主选文明推荐'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'全62文明总名次'!$A$1:$F$63</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'全62文明总名次'!$1:$1</definedName>
@@ -576,7 +576,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；巨型投石机科技树 9/12；缺 建筑学、囤积、采石场；最直接一条：帖木儿攻城术（巨型投石机射程+2）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；巨型投石机科技树 9/12；缺 建筑学、囤积、采石场；最直接一条：帖木儿攻城术（巨型投石机射程+2）</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 1 / 弱 0）；巨型投石机科技树 9/12；缺 建筑学、采石场、灼热箭；最直接一条：配重块（巨型投石机/投石车系攻+15%）</t>
+          <t>备选：阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；巨型投石机科技树 9/12；缺 建筑学、采石场、灼热箭；最直接一条：配重块（巨型投石机/投石车系攻+15%）</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       <c r="C4" s="4" t="inlineStr"/>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 1 / 弱 0）；巨型投石机科技树 8/12；缺 巨型投石机、攻城工程技师、工兵、囤积；最直接一条：卧虎（牵引抛石机/楼船巨型投石武器发更多弹药）</t>
+          <t>备选：阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；巨型投石机科技树 8/12；缺 巨型投石机、攻城工程技师、工兵、囤积；最直接一条：卧虎（牵引抛石机/楼船巨型投石武器发更多弹药）</t>
         </is>
       </c>
     </row>
@@ -632,35 +632,35 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；巨型投石机科技树 11/12；缺 采石场；最直接一条：战狼号（巨型投石机可造成爆炸伤害且更准）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；巨型投石机科技树 11/12；缺 采石场；最直接一条：战狼号（巨型投石机可造成爆炸伤害且更准）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="51" customHeight="1">
       <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>魏（备选）</t>
+          <t>匈奴（备选）</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 1 / 弱 0）；巨型投石机科技树 8/12；缺 巨型投石机、攻城工程技师、建筑学、工兵；最直接一条：牵引抛石机/楼船费用-25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
+          <t>备选：阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；巨型投石机科技树 7/12；缺 攻城工程技师、建筑学、囤积、采石场；最直接一条：巨型投石机攻单位/小目标更准</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="51" customHeight="1">
       <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>匈奴（备选）</t>
+          <t>魏（备选）</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 1 / 弱 0）；巨型投石机科技树 7/12；缺 攻城工程技师、建筑学、囤积、采石场；最直接一条：巨型投石机攻单位/小目标更准</t>
+          <t>备选：阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；巨型投石机科技树 8/12；缺 巨型投石机、攻城工程技师、建筑学、工兵；最直接一条：牵引抛石机/楼船费用-25%</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr"/>
     </row>
-    <row r="10" ht="36" customHeight="1">
+    <row r="10" ht="51" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>第 3 位</t>
@@ -688,15 +688,23 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；巨型投石机科技树 8/12；缺 建筑学、工兵、采石场、灼热箭；最直接一条：弹射器（巨型投石机攻速和组装/拆装提升）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；巨型投石机科技树 8/12；缺 建筑学、工兵、采石场、灼热箭；最直接一条：弹射器（巨型投石机攻速和组装/拆装提升）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>葡萄牙（备选）</t>
+        </is>
+      </c>
       <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>备选：阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；巨型投石机科技树 11/12；缺 囤积</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="2" t="inlineStr"/>
@@ -722,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -765,7 +773,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="51" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>4</v>
       </c>
@@ -791,7 +799,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；巨型投石机科技树 9/12；缺 建筑学、采石场、灼热箭；最直接一条：配重块（巨型投石机/投石车系攻+15%）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；巨型投石机科技树 9/12；缺 建筑学、采石场、灼热箭；最直接一条：配重块（巨型投石机/投石车系攻+15%）</t>
         </is>
       </c>
     </row>
@@ -821,17 +829,17 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；巨型投石机科技树 8/12；缺 巨型投石机、攻城工程技师、工兵、囤积；最直接一条：卧虎（牵引抛石机/楼船巨型投石武器发更多弹药）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；巨型投石机科技树 8/12；缺 巨型投石机、攻城工程技师、工兵、囤积；最直接一条：卧虎（牵引抛石机/楼船巨型投石武器发更多弹药）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="51" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>匈奴</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -841,7 +849,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>牵引抛石机/楼船费用-25%</t>
+          <t>巨型投石机攻单位/小目标更准</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -851,17 +859,17 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；巨型投石机科技树 8/12；缺 巨型投石机、攻城工程技师、建筑学、工兵；最直接一条：牵引抛石机/楼船费用-25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；巨型投石机科技树 7/12；缺 攻城工程技师、建筑学、囤积、采石场；最直接一条：巨型投石机攻单位/小目标更准</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="51" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>匈奴</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -871,7 +879,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>巨型投石机攻单位/小目标更准</t>
+          <t>牵引抛石机/楼船费用-25%</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -881,12 +889,42 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；巨型投石机科技树 7/12；缺 攻城工程技师、建筑学、囤积、采石场；最直接一条：巨型投石机攻单位/小目标更准</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；巨型投石机科技树 8/12；缺 巨型投石机、攻城工程技师、建筑学、工兵；最直接一条：牵引抛石机/楼船费用-25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>所有单位黄金费用-20%</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>无条件</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；巨型投石机科技树 11/12；缺 囤积</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F5"/>
+  <autoFilter ref="A1:F6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1110,7 +1148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1174,8 +1212,35 @@
         </is>
       </c>
     </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>所有单位黄金费用-20%</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E2"/>
+  <autoFilter ref="A1:E3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1187,7 +1252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1881,12 +1946,12 @@
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>海军和火药文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1896,19 +1961,19 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>海军和火药文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「采果工产食+木材」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「牧场取代农田」）</t>
         </is>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>骑兵和骆驼文明</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1918,19 +1983,19 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「牧场取代农田」）</t>
+          <t>骑兵和骆驼文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「开局2果树丛」）</t>
         </is>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
+          <t>撒克逊人</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>骑兵和骆驼文明</t>
+          <t>步兵和防御文明</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1940,19 +2005,19 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>骑兵和骆驼文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「开局2果树丛」）</t>
+          <t>步兵和防御文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
         </is>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>撒克逊人</t>
+          <t>蜀</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>步兵和防御文明</t>
+          <t>弓兵和攻城文明</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1962,19 +2027,19 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>步兵和防御文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
+          <t>弓兵和攻城文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「伐木工产木+食物」）</t>
         </is>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>斯拉夫</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>弓兵和攻城文明</t>
+          <t>步兵和攻城文明</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -1984,19 +2049,19 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>弓兵和攻城文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「伐木工产木+食物」）</t>
+          <t>步兵和攻城文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「农民工作速度+15%」）</t>
         </is>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
+          <t>条顿</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>步兵和攻城文明</t>
+          <t>步兵和防御文明</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2006,19 +2071,19 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「农民工作速度+15%」）</t>
+          <t>步兵和防御文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「农田费用-40%」）</t>
         </is>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>条顿</t>
+          <t>图皮</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>步兵和防御文明</t>
+          <t>弓兵与步兵文明</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2028,19 +2093,19 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>步兵和防御文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「农田费用-40%」）</t>
+          <t>弓兵与步兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「开局每种资源+25」）</t>
         </is>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>弓兵与步兵文明</t>
+          <t>火药文明</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2050,19 +2115,19 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>弓兵与步兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「开局每种资源+25」）</t>
+          <t>火药文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「金矿工速度+25%」）</t>
         </is>
       </c>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>火药文明</t>
+          <t>骑兵和海军文明</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2072,19 +2137,19 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>火药文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「金矿工速度+25%」）</t>
+          <t>骑兵和海军文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
         </is>
       </c>
     </row>
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>骑兵和海军文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2094,19 +2159,19 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>骑兵和海军文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「独轮推车/手推车免费」）</t>
         </is>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>火药和僧侣文明</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2116,19 +2181,19 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「独轮推车/手推车免费」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「建筑工速度+30%」）</t>
         </is>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>火药和僧侣文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2138,19 +2203,19 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「建筑工速度+30%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「初始石料+100」）</t>
         </is>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>亚美尼亚</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2160,19 +2225,19 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「初始石料+100」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「骡车费用-25%」）</t>
         </is>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>亚美尼亚</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>弓兵和海军文明</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -2182,19 +2247,19 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「骡车费用-25%」）</t>
+          <t>弓兵和海军文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「升时代费用-15%」）</t>
         </is>
       </c>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>印度斯坦</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>弓兵和海军文明</t>
+          <t>骆驼和火药文明</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2204,19 +2269,19 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>弓兵和海军文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「升时代费用-15%」）</t>
+          <t>骆驼和火药文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
         </is>
       </c>
     </row>
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>印度斯坦</t>
+          <t>印加</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>骆驼和火药文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2226,19 +2291,19 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>骆驼和火药文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「房屋/聚落人口+5」）</t>
         </is>
       </c>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>印加</t>
+          <t>越南</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>弓兵文明</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -2248,19 +2313,19 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「房屋/聚落人口+5」）</t>
+          <t>弓兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「开局显示敌方TC」）</t>
         </is>
       </c>
     </row>
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>越南</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>弓兵文明</t>
+          <t>步弓手和火药文明</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -2270,19 +2335,19 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>弓兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「开局显示敌方TC」）</t>
+          <t>步弓手和火药文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「初始村民+3，木材-50，食物-200」）</t>
         </is>
       </c>
     </row>
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>步弓手和火药文明</t>
+          <t>弓兵和骑兵文明</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -2292,19 +2357,19 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>步弓手和火药文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「初始村民+3，木材-50，食物-200」）</t>
+          <t>弓兵和骑兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「造船厂工作速度+15%」）</t>
         </is>
       </c>
     </row>
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>弓兵和骑兵文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -2314,19 +2379,19 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>弓兵和骑兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「造船厂工作速度+15%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「高地受伤-10%」）</t>
         </is>
       </c>
     </row>
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>弓兵和象兵文明</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -2336,19 +2401,19 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「高地受伤-10%」）</t>
+          <t>弓兵和象兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「采石村民缓慢获食」）</t>
         </is>
       </c>
     </row>
     <row r="53" ht="36" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>普鲁人</t>
+          <t>色雷斯人</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>弓兵和象兵文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -2358,14 +2423,14 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>弓兵和象兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「采石村民缓慢获食」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「精锐掷矛手升级免费」）</t>
         </is>
       </c>
     </row>
     <row r="54" ht="36" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>色雷斯人</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2380,19 +2445,19 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「精锐掷矛手升级免费」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「进入市政/古典免费获一军事执政官」）</t>
         </is>
       </c>
     </row>
     <row r="55" ht="36" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>雅典</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -2402,34 +2467,12 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「进入市政/古典免费获一军事执政官」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="36" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>雅典</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>步兵和海军文明</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强巨型投石机</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
           <t>步兵和海军文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「TC可切换政策风格（经济/海军/军事）」）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D56"/>
+  <autoFilter ref="A1:D55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -2441,7 +2484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2609,22 +2652,22 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>匈奴</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8/12</t>
+          <t>7/12</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>牵引抛石机/楼船费用-25%</t>
+          <t>巨型投石机攻单位/小目标更准</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；巨型投石机科技树 8/12。缺：巨型投石机、攻城工程技师、建筑学、工兵</t>
+          <t>原生条目 1 条（强 1）；巨型投石机科技树 7/12。缺：攻城工程技师、建筑学、囤积、采石场、灼热箭</t>
         </is>
       </c>
     </row>
@@ -2634,27 +2677,52 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>匈奴</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7/12</t>
+          <t>8/12</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>巨型投石机攻单位/小目标更准</t>
+          <t>牵引抛石机/楼船费用-25%</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；巨型投石机科技树 7/12。缺：攻城工程技师、建筑学、囤积、采石场、灼热箭</t>
+          <t>原生条目 1 条（强 1）；巨型投石机科技树 8/12。缺：巨型投石机、攻城工程技师、建筑学、工兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>11/12</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>所有单位黄金费用-20%</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>原生条目 1 条（强 0）；巨型投石机科技树 11/12。缺：囤积</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E8"/>
+  <autoFilter ref="A1:E9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -2735,7 +2803,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；巨型投石机科技树 9/12；缺 建筑学、囤积、采石场；最直接一条：帖木儿攻城术（巨型投石机射程+2）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；巨型投石机科技树 9/12；缺 建筑学、囤积、采石场；最直接一条：帖木儿攻城术（巨型投石机射程+2）</t>
         </is>
       </c>
     </row>
@@ -2765,11 +2833,11 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；巨型投石机科技树 11/12；缺 采石场；最直接一条：战狼号（巨型投石机可造成爆炸伤害且更准）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；巨型投石机科技树 11/12；缺 采石场；最直接一条：战狼号（巨型投石机可造成爆炸伤害且更准）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="51" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -2795,11 +2863,11 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；巨型投石机科技树 8/12；缺 建筑学、工兵、采石场、灼热箭；最直接一条：弹射器（巨型投石机攻速和组装/拆装提升）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；巨型投石机科技树 8/12；缺 建筑学、工兵、采石场、灼热箭；最直接一条：弹射器（巨型投石机攻速和组装/拆装提升）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="51" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -2825,7 +2893,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；巨型投石机科技树 9/12；缺 建筑学、采石场、灼热箭；最直接一条：配重块（巨型投石机/投石车系攻+15%）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；巨型投石机科技树 9/12；缺 建筑学、采石场、灼热箭；最直接一条：配重块（巨型投石机/投石车系攻+15%）</t>
         </is>
       </c>
     </row>
@@ -2855,17 +2923,17 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；巨型投石机科技树 8/12；缺 巨型投石机、攻城工程技师、工兵、囤积；最直接一条：卧虎（牵引抛石机/楼船巨型投石武器发更多弹药）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；巨型投石机科技树 8/12；缺 巨型投石机、攻城工程技师、工兵、囤积；最直接一条：卧虎（牵引抛石机/楼船巨型投石武器发更多弹药）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="51" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>匈奴</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -2880,22 +2948,22 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>牵引抛石机/楼船费用-25%</t>
+          <t>巨型投石机攻单位/小目标更准</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；巨型投石机科技树 8/12；缺 巨型投石机、攻城工程技师、建筑学、工兵；最直接一条：牵引抛石机/楼船费用-25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；巨型投石机科技树 7/12；缺 攻城工程技师、建筑学、囤积、采石场；最直接一条：巨型投石机攻单位/小目标更准</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="51" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>匈奴</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2910,12 +2978,12 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>巨型投石机攻单位/小目标更准</t>
+          <t>牵引抛石机/楼船费用-25%</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；巨型投石机科技树 7/12；缺 攻城工程技师、建筑学、囤积、采石场；最直接一条：巨型投石机攻单位/小目标更准</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；巨型投石机科技树 8/12；缺 巨型投石机、攻城工程技师、建筑学、工兵；最直接一条：牵引抛石机/楼船费用-25%</t>
         </is>
       </c>
     </row>
@@ -2925,27 +2993,27 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>阿兹特克</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>不建议</t>
+          <t>2000 金</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>无一条直接加强巨型投石机</t>
+          <t>所有单位黄金费用-20%</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>步兵和僧侣文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「初始黄金+50」）</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；巨型投石机科技树 11/12；缺 囤积</t>
         </is>
       </c>
     </row>
@@ -2955,7 +3023,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>埃塞俄比亚</t>
+          <t>阿兹特克</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -2975,7 +3043,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>弓兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「升时代获得黄金+100、食物+100」）</t>
+          <t>步兵和僧侣文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「初始黄金+50」）</t>
         </is>
       </c>
     </row>
@@ -2985,7 +3053,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>埃塞俄比亚</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3005,7 +3073,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>骑兵和海军文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「村民黑暗移速+5%，封建起+10%」）</t>
+          <t>弓兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「升时代获得黄金+100、食物+100」）</t>
         </is>
       </c>
     </row>
@@ -3015,7 +3083,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3035,7 +3103,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>防御文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「建筑黑暗/封建/城堡/帝王生命+10/20/30/40%」）</t>
+          <t>骑兵和海军文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「村民黑暗移速+5%，封建起+10%」）</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3113,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>保加利亚</t>
+          <t>拜占庭</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3065,7 +3133,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「民兵系升级免费」）</t>
+          <t>防御文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「建筑黑暗/封建/城堡/帝王生命+10/20/30/40%」）</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3143,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
+          <t>保加利亚</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -3095,7 +3163,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「大庄园替代磨坊」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「民兵系升级免费」）</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3173,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -3125,7 +3193,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「初始木材/食物+50」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「大庄园替代磨坊」）</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3203,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>波希米亚</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -3155,7 +3223,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「采矿场科技免费」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「初始木材/食物+50」）</t>
         </is>
       </c>
     </row>
@@ -3165,7 +3233,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>勃艮第</t>
+          <t>波希米亚</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -3185,7 +3253,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「采矿场科技免费」）</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3263,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼</t>
+          <t>勃艮第</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -3215,7 +3283,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「渔夫/捕鱼船携带+15」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3293,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -3245,7 +3313,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「捕鱼船/村民存食+5%」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「渔夫/捕鱼船携带+15」）</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3323,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>丹麦人</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -3275,7 +3343,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「采果工速度+15%」）</t>
+          <t>步兵和攻城文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「捕鱼船/村民存食+5%」）</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3353,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -3305,7 +3373,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>防御和海军文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「石矿工速度+20%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「采果工速度+15%」）</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3383,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>高棉</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -3335,7 +3403,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>攻城武器和大象文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「无需建筑即可升时代/解锁建筑」）</t>
+          <t>防御和海军文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「石矿工速度+20%」）</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3413,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>哥特</t>
+          <t>高棉</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -3365,7 +3433,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「可立即研究织布机」）</t>
+          <t>攻城武器和大象文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「无需建筑即可升时代/解锁建筑」）</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3443,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
+          <t>哥特</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -3395,7 +3463,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>防御和骑兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「开局有骡车」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「可立即研究织布机」）</t>
         </is>
       </c>
     </row>
@@ -3405,7 +3473,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>凯尔特</t>
+          <t>格鲁吉亚</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -3425,7 +3493,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城武器文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「伐木工速度+15%」）</t>
+          <t>防御和骑兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「开局有骡车」）</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3503,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>凯尔特</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -3455,7 +3523,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「封建可额外建一座TC」）</t>
+          <t>步兵和攻城武器文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「伐木工速度+15%」）</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3533,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>立陶宛</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -3485,7 +3553,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>骑兵和僧侣文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「每座TC食物+100」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「封建可额外建一座TC」）</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3563,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>立陶宛</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -3515,7 +3583,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
+          <t>骑兵和僧侣文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「每座TC食物+100」）</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3593,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -3545,7 +3613,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>海军文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「升时代速度+66%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3623,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>马里</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3575,7 +3643,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「建筑木材-15%」）</t>
+          <t>海军文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「升时代速度+66%」）</t>
         </is>
       </c>
     </row>
@@ -3585,7 +3653,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>马里</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -3605,7 +3673,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>骑兵与反制单位文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「采果工存食+25%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「建筑木材-15%」）</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3683,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -3635,7 +3703,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「村民一击杀狼」）</t>
+          <t>骑兵与反制单位文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「采果工存食+25%」）</t>
         </is>
       </c>
     </row>
@@ -3645,7 +3713,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>玛雅</t>
+          <t>马扎尔</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -3665,7 +3733,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>弓兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「开局村民+1，食物-50」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「村民一击杀狼」）</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3743,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>蒙古</t>
+          <t>玛雅</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -3695,7 +3763,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>骑射手文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「猎人速度+40%」）</t>
+          <t>弓兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「开局村民+1，食物-50」）</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3773,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>蒙古</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -3725,7 +3793,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>象兵和海军文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「升时代TC产生2村民」）</t>
+          <t>骑射手文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「猎人速度+40%」）</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3803,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>缅甸</t>
+          <t>孟加拉</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -3755,7 +3823,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「伐木场科技免费」）</t>
+          <t>象兵和海军文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「升时代TC产生2村民」）</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3833,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>穆伊斯卡</t>
+          <t>缅甸</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -3785,7 +3853,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「升时代黄金-50%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「伐木场科技免费」）</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3863,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>穆伊斯卡</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
@@ -3815,7 +3883,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>骑兵和火药文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
+          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「升时代黄金-50%」）</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3893,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -3845,7 +3913,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>海军和火药文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「采果工产食+木材」）</t>
+          <t>骑兵和火药文明；本表 450 条中无一条直接作用于巨型投石机。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4701,101 +4769,141 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>① 只看直接作用于巨型投石机本体、或其前置/费用/产出的条目；</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="10" t="inlineStr"/>
+          <t>本表按用户打法口径分四个阶段排序：先加强要玩的主流派兵种，再减它的资源消耗，最后才补资源效率。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>① 阶段 1 · 本体强化</t>
+        </is>
+      </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>② 泛用条目与兵种类一律剔除（放进「与巨型投石机流无关·可跳过」）；</t>
+          <t>直接加强巨型投石机本体的条目（攻击/护甲/生命/攻速/射程/移速/回血/数量/生产训练速度/解锁升级等）。这一档最优先。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="10" t="inlineStr"/>
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>② 阶段 2 · 减费用</t>
+        </is>
+      </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>③ 门槛越低、替代成本越高，名次越靠前。</t>
+          <t>降低该兵种及同系兵种（攻城武器厂单位）生产所需资源的条目：费用/成本 -N%、升级免费、用其它资源替代。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="10" t="inlineStr"/>
-      <c r="B15" s="10" t="inlineStr"/>
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>③ 阶段 3 · 资源效率</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>采集/产出/携带/贸易/人口/经济科技等让主流派更快成型的条目。</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>未验证项</t>
+          <t>④ 阶段 4 · 其他相关</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>本表的档位与名次为依据「条目文本 + 官方科技树」的经验判断，未逐项实测；与实战不符时以实战为准。</t>
+          <t>其余与本流派相关、但不属于上述三类的条目。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>★ 最重要的一条：别买重复</t>
-        </is>
-      </c>
+      <c r="A17" s="10" t="inlineStr"/>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>主选文明已经自带的加成，不要再用按钮买一遍——一个按钮只能研究一次，重复等于白花 2000 金。</t>
+          <t>同阶段内按「人工权威顺序（实战强度）」再排；泛用条目与兵种类一律剔除（放进「与巨型投石机流无关·可跳过」）。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="10" t="inlineStr"/>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>正确流程是：先定主选文明（见「主选文明推荐」），再按剩下的缺口挑 3 个免费位。</t>
-        </is>
-      </c>
+      <c r="B18" s="10" t="inlineStr"/>
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>数据来源</t>
+          <t>未验证项</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
+          <t>本表的档位与名次为依据「条目文本 + 官方科技树」的经验判断，未逐项实测；与实战不符时以实战为准。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="10" t="inlineStr"/>
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>★ 最重要的一条：别买重复</t>
+        </is>
+      </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
+          <t>主选文明已经自带的加成，不要再用按钮买一遍——一个按钮只能研究一次，重复等于白花 2000 金。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>整理</t>
-        </is>
-      </c>
+      <c r="A21" s="10" t="inlineStr"/>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>By RemonBo；本表由 DSH 生成。</t>
+          <t>正确流程是：先定主选文明（见「主选文明推荐」），再按剩下的缺口挑 3 个免费位。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="10" t="inlineStr">
         <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="10" t="inlineStr"/>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>整理</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>By RemonBo；本表由 DSH 生成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
           <t>与本表配套</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>同目录下的箭塔流、炮塔流与其余流派总表。</t>
         </is>
